--- a/Security-data/data/output/ndss_2025_us_institutions.xlsx
+++ b/Security-data/data/output/ndss_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5943,7 +5943,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Jinhao Zhu</t>
+          <t>Xiangzhe Xu</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5951,22 +5951,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>NDSS-VulShield: Protecting Vulnerable Code Before Deploying Patches.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>UC Berkeley</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Sena Sahin</t>
+          <t>Zhuo Zhang 0002</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5974,22 +5974,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Burak Sahin</t>
+          <t>Zian Su</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5997,22 +5997,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Frank Li 0001</t>
+          <t>Ziyang Huang 0004</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6020,22 +6020,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Xiaoyan Sun 0003</t>
+          <t>Shiwei Feng 0002</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6043,13 +6043,312 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>NDSS-What's Done Is Not What's Claimed: Detecting and Interpreting Inconsistencies in App Behaviors.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D245" t="n">
         <v>4</v>
       </c>
       <c r="E245" t="inlineStr">
+        <is>
+          <t>Purdue University</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Yapeng Ye</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>5</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Purdue University</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Nan Jiang 0012</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>6</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Purdue University</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Danning Xie</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>7</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Purdue University</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Siyuan Cheng 0005</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>8</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Purdue University</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Lin Tan 0001</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>9</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Purdue University</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Xiangyu Zhang 0001</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>10</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Purdue University</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Maryam Abbasihafshejani</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>University of Texas at San Antonio</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Murtuza Jadliwala</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>5</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>University of Texas at San Antonio</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Jinhao Zhu</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>NDSS-VulShield: Protecting Vulnerable Code Before Deploying Patches.</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>2</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>UC Berkeley</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Sena Sahin</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Burak Sahin</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Frank Li 0001</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>2</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Xiaoyan Sun 0003</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>NDSS-What's Done Is Not What's Claimed: Detecting and Interpreting Inconsistencies in App Behaviors.</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>4</v>
+      </c>
+      <c r="E258" t="inlineStr">
         <is>
           <t>Department of Computer Science, Worcester Polytechnic Institute</t>
         </is>

--- a/Security-data/data/output/ndss_2025_us_institutions.xlsx
+++ b/Security-data/data/output/ndss_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:E264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2171,7 +2171,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jin Yao</t>
+          <t>Patrick D. McDaniel</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2179,22 +2179,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NDSS-TrajDeleter: Enabling Trajectory Forgetting in Offline Reinforcement Learning Agents.</t>
+          <t>NDSS-Secure IP Address Allocation at Cloud Scale.</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Jin Yao</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Xiaoyuan Wu</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NDSS-Transparency or Information Overload? Evaluating Users' Comprehension and Perceptions of the iOS App Privacy Report.</t>
+          <t>NDSS-TrajDeleter: Enabling Trajectory Forgetting in Offline Reinforcement Learning Agents.</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Lydia Hu</t>
+          <t>Xiaoyuan Wu</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Eric Zeng 0001</t>
+          <t>Lydia Hu</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hana Habib</t>
+          <t>Eric Zeng 0001</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Lujo Bauer</t>
+          <t>Hana Habib</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Yuqing Yang 0003</t>
+          <t>Lujo Bauer</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2340,22 +2340,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NDSS-Understanding Miniapp Malware: Identification, Dissection, and Characterization.</t>
+          <t>NDSS-Transparency or Information Overload? Evaluating Users' Comprehension and Perceptions of the iOS App Privacy Report.</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Yue Zhang 0025</t>
+          <t>Yuqing Yang 0003</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2367,18 +2367,18 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Drexel University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Yue Zhang 0025</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2390,18 +2390,18 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Drexel University</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Hongwei Wu</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2409,22 +2409,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NDSS-VeriBin: Adaptive Verification of Patches at the Binary Level.</t>
+          <t>NDSS-Understanding Miniapp Malware: Identification, Dissection, and Characterization.</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ruoyu Wu</t>
+          <t>Hongwei Wu</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ayushi Sharma</t>
+          <t>Ruoyu Wu</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Aravind Machiry</t>
+          <t>Ayushi Sharma</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Aravind Machiry</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Jackson Sippe</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NDSS-Wallbleed: A Memory Disclosure Vulnerability in the Great Firewall of China.</t>
+          <t>NDSS-VeriBin: Adaptive Verification of Patches at the Binary Level.</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>University of Colorado Boulder</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jade Sheffey</t>
+          <t>Jackson Sippe</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2551,18 +2551,18 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UMass Amherst</t>
+          <t>University of Colorado Boulder</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Jade Sheffey</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Eric Wustrow</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>University of Colorado Boulder</t>
+          <t>UMass Amherst</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Stijn Pletinckx</t>
+          <t>Eric Wustrow</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2616,22 +2616,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NDSS-A Large-Scale Measurement Study of the PROXY Protocol and its Security Implications.</t>
+          <t>NDSS-Wallbleed: A Memory Disclosure Vulnerability in the Great Firewall of China.</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>University of California, Santa Barbara</t>
+          <t>University of Colorado Boulder</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Christopher Kruegel</t>
+          <t>Stijn Pletinckx</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Giovanni Vigna</t>
+          <t>Christopher Kruegel</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mahsa Bastankhah</t>
+          <t>Giovanni Vigna</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NDSS-Alba: The Dawn of Scalable Bridges for Blockchains.</t>
+          <t>NDSS-A Large-Scale Measurement Study of the PROXY Protocol and its Security Implications.</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -2693,14 +2693,14 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of California, Santa Barbara</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Dominik Wermke</t>
+          <t>Mahsa Bastankhah</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2708,22 +2708,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NDSS-Attributing Open-Source Contributions is Critical but Difficult: A Systematic Analysis of GitHub Practices and Their Impact on Software Supply Chain Security.</t>
+          <t>NDSS-Alba: The Dawn of Scalable Bridges for Blockchains.</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Linxi Jiang</t>
+          <t>Dominik Wermke</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NDSS-Beyond Classification: Inferring Function Names in Stripped Binaries via Domain Adapted LLMs.</t>
+          <t>NDSS-Attributing Open-Source Contributions is Critical but Difficult: A Systematic Analysis of GitHub Practices and Their Impact on Software Supply Chain Security.</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Xin Jin</t>
+          <t>Linxi Jiang</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Xin Jin</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ming Zhao</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2800,22 +2800,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NDSS-Blackbox Fuzzing of Distributed Systems with Multi-Dimensional Inputs and Symmetry-Based Feedback Pruning.</t>
+          <t>NDSS-Beyond Classification: Inferring Function Names in Stripped Binaries via Domain Adapted LLMs.</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Caihua Li</t>
+          <t>Ming Zhao</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NDSS-Blindfold: Confidential Memory Management by Untrusted Operating System.</t>
+          <t>NDSS-Blackbox Fuzzing of Distributed Systems with Multi-Dimensional Inputs and Symmetry-Based Feedback Pruning.</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Seung-Seob Lee</t>
+          <t>Caihua Li</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Lin Zhong 0001</t>
+          <t>Seung-Seob Lee</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Magdalena Pasternak</t>
+          <t>Lin Zhong 0001</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2892,22 +2892,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NDSS-Characterizing the Impact of Audio Deepfakes in the Presence of Cochlear Implant.</t>
+          <t>NDSS-Blindfold: Confidential Memory Management by Untrusted Operating System.</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kevin Warren</t>
+          <t>Magdalena Pasternak</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Daniel Olszewski</t>
+          <t>Kevin Warren</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Susan Nittrouer</t>
+          <t>Daniel Olszewski</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Patrick Traynor</t>
+          <t>Susan Nittrouer</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Chaithanya Naik Mude</t>
+          <t>Patrick Traynor</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3007,22 +3007,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NDSS-Crosstalk-induced Side Channel Threats in Multi-Tenant NISQ Computers.</t>
+          <t>NDSS-Characterizing the Impact of Audio Deepfakes in the Presence of Cochlear Implant.</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sanjay Das</t>
+          <t>Kevin R. B. Butler</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NDSS-Crosstalk-induced Side Channel Threats in Multi-Tenant NISQ Computers.</t>
+          <t>NDSS-Characterizing the Impact of Audio Deepfakes in the Presence of Cochlear Implant.</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Preetham Chandra Tikkireddi</t>
+          <t>Chaithanya Naik Mude</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Swamit Tannu</t>
+          <t>Sanjay Das</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3080,18 +3080,18 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>University of Wisconsin, Madison</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kanad Basu</t>
+          <t>Preetham Chandra Tikkireddi</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3103,18 +3103,18 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>University of Wisconsin-Madison</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Christopher Ellis</t>
+          <t>Swamit Tannu</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NDSS-Deanonymizing Device Identities via Side-channel Attacks in Exclusive-use IoTs &amp; Mitigation.</t>
+          <t>NDSS-Crosstalk-induced Side Channel Threats in Multi-Tenant NISQ Computers.</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Wisconsin, Madison</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Yue Zhang 0025</t>
+          <t>Kanad Basu</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3145,22 +3145,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NDSS-Deanonymizing Device Identities via Side-channel Attacks in Exclusive-use IoTs &amp; Mitigation.</t>
+          <t>NDSS-Crosstalk-induced Side Channel Threats in Multi-Tenant NISQ Computers.</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Drexel University</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Mohit Kumar Jangid</t>
+          <t>Christopher Ellis</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Shixuan Zhao 0002</t>
+          <t>Yue Zhang 0025</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3195,18 +3195,18 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Drexel University</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Mohit Kumar Jangid</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ziming Zhao 0001</t>
+          <t>Shixuan Zhao 0002</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3237,22 +3237,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NDSS-Defending Against Membership Inference Attacks on Iteratively Pruned Deep Neural Networks.</t>
+          <t>NDSS-Deanonymizing Device Identities via Side-channel Attacks in Exclusive-use IoTs &amp; Mitigation.</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tyler Tucker</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3260,22 +3260,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
+          <t>NDSS-Deanonymizing Device Identities via Side-channel Attacks in Exclusive-use IoTs &amp; Mitigation.</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Nathaniel Bennett</t>
+          <t>Md. Armanuzzaman</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3283,22 +3283,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
+          <t>NDSS-Defending Against Membership Inference Attacks on Iteratively Pruned Deep Neural Networks.</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Patrick Traynor</t>
+          <t>Ziming Zhao 0001</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
+          <t>NDSS-Defending Against Membership Inference Attacks on Iteratively Pruned Deep Neural Networks.</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -3314,14 +3314,14 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Peng Liu 0005</t>
+          <t>Tyler Tucker</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3329,22 +3329,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NDSS-Eclipse Attacks on Monero's Peer-to-Peer Network.</t>
+          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Penn State University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Omar Alrawi</t>
+          <t>Nathaniel Bennett</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NDSS-Evaluating Machine Learning-Based IoT Device Identification Models for Security Applications.</t>
+          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Connor Glosner</t>
+          <t>Kevin R. B. Butler</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3375,22 +3375,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NDSS-FUZZUER: Enabling Fuzzing of UEFI Interfaces on EDK-2.</t>
+          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Aravind Machiry</t>
+          <t>Patrick Traynor</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3398,22 +3398,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NDSS-FUZZUER: Enabling Fuzzing of UEFI Interfaces on EDK-2.</t>
+          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Qi Ling</t>
+          <t>Peng Liu 0005</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NDSS-GadgetMeter: Quantitatively and Accurately Gauging the Exploitability of Speculative Gadgets.</t>
+          <t>NDSS-Eclipse Attacks on Monero's Peer-to-Peer Network.</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Penn State University</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Baris Kasikci</t>
+          <t>Omar Alrawi</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3444,22 +3444,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NDSS-GadgetMeter: Quantitatively and Accurately Gauging the Exploitability of Speculative Gadgets.</t>
+          <t>NDSS-Evaluating Machine Learning-Based IoT Device Identification Models for Security Applications.</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>University of Washington and Google</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Xiaojiang Du</t>
+          <t>Connor Glosner</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3467,22 +3467,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NDSS-Hidden and Lost Control: on Security Design Risks in IoT User-Facing Matter Controller.</t>
+          <t>NDSS-FUZZUER: Enabling Fuzzing of UEFI Interfaces on EDK-2.</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Runze Zhang</t>
+          <t>Aravind Machiry</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3490,22 +3490,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
+          <t>NDSS-FUZZUER: Enabling Fuzzing of UEFI Interfaces on EDK-2.</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Mingxuan Yao</t>
+          <t>Qi Ling</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3513,22 +3513,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
+          <t>NDSS-GadgetMeter: Quantitatively and Accurately Gauging the Exploitability of Speculative Gadgets.</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Haichuan Xu</t>
+          <t>Baris Kasikci</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
+          <t>NDSS-GadgetMeter: Quantitatively and Accurately Gauging the Exploitability of Speculative Gadgets.</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Washington and Google</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Omar Alrawi</t>
+          <t>Xiaojiang Du</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3559,22 +3559,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
+          <t>NDSS-Hidden and Lost Control: on Security Design Risks in IoT User-Facing Matter Controller.</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Runze Zhang</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Corban Villa</t>
+          <t>Mingxuan Yao</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3605,22 +3605,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
+          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Constantine Doumanidis</t>
+          <t>Haichuan Xu</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
+          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Hithem Lamri</t>
+          <t>Omar Alrawi</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
+          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Michail Maniatakos</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
+          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Franziska Roesner</t>
+          <t>Corban Villa</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NDSS-IsolateGPT: An Execution Isolation Architecture for LLM-Based Agentic Systems.</t>
+          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Tadayoshi Kohno</t>
+          <t>Constantine Doumanidis</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3720,22 +3720,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NDSS-IsolateGPT: An Execution Isolation Architecture for LLM-Based Agentic Systems.</t>
+          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Yue Xiao 0007</t>
+          <t>Hithem Lamri</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3743,22 +3743,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
+          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Dhilung Kirat</t>
+          <t>Michail Maniatakos</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
+          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Douglas Lee Schales</t>
+          <t>Franziska Roesner</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
+          <t>NDSS-IsolateGPT: An Execution Isolation Architecture for LLM-Based Agentic Systems.</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Jiyong Jang</t>
+          <t>Tadayoshi Kohno</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3812,22 +3812,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
+          <t>NDSS-IsolateGPT: An Execution Isolation Architecture for LLM-Based Agentic Systems.</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Piyush Kumar Sharma</t>
+          <t>Yue Xiao 0007</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3835,22 +3835,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NDSS-LAMP: Lightweight Approaches for Latency Minimization in Mixnets with Practical Deployment Considerations.</t>
+          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Kushal Babel</t>
+          <t>Dhilung Kirat</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
+          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Cornell Tech &amp;amp; IC3</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Andrey Chursin</t>
+          <t>Douglas Lee Schales</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3881,22 +3881,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
+          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Mysten Labs</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Anastasios Kichidis</t>
+          <t>Jiyong Jang</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
+          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -3912,14 +3912,14 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Mysten Labs</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Arun Koshy</t>
+          <t>Piyush Kumar Sharma</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3927,22 +3927,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
+          <t>NDSS-LAMP: Lightweight Approaches for Latency Minimization in Mixnets with Practical Deployment Considerations.</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Mysten Labs</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mingwei Tian</t>
+          <t>Kushal Babel</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3954,18 +3954,18 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Mysten Labs</t>
+          <t>Cornell Tech &amp;amp; IC3</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Darion Cassel</t>
+          <t>Andrey Chursin</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3973,22 +3973,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
+          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Mysten Labs</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Min-Chien Hsu</t>
+          <t>Anastasios Kichidis</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
+          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Mysten Labs</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ruben Martins</t>
+          <t>Arun Koshy</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4019,22 +4019,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
+          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Mysten Labs</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Limin Jia 0001</t>
+          <t>Mingwei Tian</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4042,22 +4042,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
+          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Mysten Labs</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ninghui Li 0001</t>
+          <t>Darion Cassel</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4065,22 +4065,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NDSS-On the Robustness of LDP Protocols for Numerical Attributes under Data Poisoning Attacks.</t>
+          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Wenhai Sun</t>
+          <t>Min-Chien Hsu</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4088,22 +4088,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>NDSS-On the Robustness of LDP Protocols for Numerical Attributes under Data Poisoning Attacks.</t>
+          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Purdue University, West Lafayette, USA</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Matthew Gregoire</t>
+          <t>Ruben Martins</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4111,22 +4111,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
+          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Margaret Pierce</t>
+          <t>Limin Jia 0001</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4134,22 +4134,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
+          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Saba Eskandarian</t>
+          <t>Ninghui Li 0001</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
+          <t>NDSS-On the Robustness of LDP Protocols for Numerical Attributes under Data Poisoning Attacks.</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Shixin Song</t>
+          <t>Wenhai Sun</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4180,22 +4180,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
+          <t>NDSS-On the Robustness of LDP Protocols for Numerical Attributes under Data Poisoning Attacks.</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Purdue University, West Lafayette, USA</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Joseph Zhang</t>
+          <t>Matthew Gregoire</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4203,22 +4203,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
+          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Mengjia Yan 0001</t>
+          <t>Margaret Pierce</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4226,22 +4226,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
+          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ruyi Ding</t>
+          <t>Saba Eskandarian</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4249,22 +4249,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
+          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Tong Zhou 0002</t>
+          <t>Shixin Song</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4272,22 +4272,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
+          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Lili Su</t>
+          <t>Joseph Zhang</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4295,22 +4295,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
+          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Aidong Adam Ding</t>
+          <t>Mengjia Yan 0001</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4318,22 +4318,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
+          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Xiaolin Xu 0001</t>
+          <t>Ruyi Ding</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Yunsi Fei</t>
+          <t>Tong Zhou 0002</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Dzung Pham 0002</t>
+          <t>Lili Su</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4387,22 +4387,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
+          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Shreyas Kulkarni</t>
+          <t>Aidong Adam Ding</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4410,22 +4410,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
+          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Xiaolin Xu 0001</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4433,22 +4433,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
+          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Peng Liu 0005</t>
+          <t>Yunsi Fei</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4456,22 +4456,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NDSS-RContainer: A Secure Container Architecture through Extending ARM CCA Hardware Primitives.</t>
+          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>The Pennsylvania State University, USA</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Shengzhi Zhang</t>
+          <t>Dzung Pham 0002</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4479,22 +4479,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NDSS-RContainer: A Secure Container Architecture through Extending ARM CCA Hardware Primitives.</t>
+          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Department of Computer Science, Metropolitan College, Boston University, USA</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Eduardo Chielle</t>
+          <t>Shreyas Kulkarni</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4502,22 +4502,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NDSS-Recurrent Private Set Intersection for Unbalanced Databases with Cuckoo Hashing and Leveled FHE.</t>
+          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Michail Maniatakos</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NDSS-Recurrent Private Set Intersection for Unbalanced Databases with Cuckoo Hashing and Leveled FHE.</t>
+          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Xin Jin</t>
+          <t>Peng Liu 0005</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4548,22 +4548,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
+          <t>NDSS-RContainer: A Secure Container Architecture through Extending ARM CCA Hardware Primitives.</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>The Pennsylvania State University, USA</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Shiqing Ma</t>
+          <t>Shengzhi Zhang</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4571,22 +4571,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
+          <t>NDSS-RContainer: A Secure Container Architecture through Extending ARM CCA Hardware Primitives.</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Department of Computer Science, Metropolitan College, Boston University, USA</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Eduardo Chielle</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4594,22 +4594,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
+          <t>NDSS-Recurrent Private Set Intersection for Unbalanced Databases with Cuckoo Hashing and Leveled FHE.</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Patrick Zielinski</t>
+          <t>Michail Maniatakos</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NDSS-Rethinking Trust in Forge-Based Git Security.</t>
+          <t>NDSS-Recurrent Private Set Intersection for Unbalanced Databases with Cuckoo Hashing and Leveled FHE.</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -4625,14 +4625,14 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Justin Cappos</t>
+          <t>Xin Jin</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4640,22 +4640,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NDSS-Rethinking Trust in Forge-Based Git Security.</t>
+          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Adrian Shuai Li</t>
+          <t>Shiqing Ma</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4663,22 +4663,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>NDSS-Revisiting Concept Drift in Windows Malware Detection: Adaptation to Real Drifted Malware with Minimal Samples.</t>
+          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Elisa Bertino</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4686,22 +4686,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>NDSS-Revisiting Concept Drift in Windows Malware Detection: Adaptation to Real Drifted Malware with Minimal Samples.</t>
+          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Shanghao Shi</t>
+          <t>Patrick Zielinski</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4709,22 +4709,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
+          <t>NDSS-Rethinking Trust in Forge-Based Git Security.</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Yang Xiao 0010</t>
+          <t>Justin Cappos</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
+          <t>NDSS-Rethinking Trust in Forge-Based Git Security.</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>University of Kentucky</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Chaoyu Zhang</t>
+          <t>Adrian Shuai Li</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4755,22 +4755,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
+          <t>NDSS-Revisiting Concept Drift in Windows Malware Detection: Adaptation to Real Drifted Malware with Minimal Samples.</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Yi Shi 0001</t>
+          <t>Elisa Bertino</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
+          <t>NDSS-Revisiting Concept Drift in Windows Malware Detection: Adaptation to Real Drifted Malware with Minimal Samples.</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Marzieh Bitaab</t>
+          <t>Shanghao Shi</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
+          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Alireza Karimi</t>
+          <t>Yang Xiao 0010</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
+          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Kentucky</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Zhuoer Lyu</t>
+          <t>Chaoyu Zhang</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4847,22 +4847,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
+          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Adam Oest</t>
+          <t>Yi Shi 0001</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4870,22 +4870,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
+          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Dhruv Kuchhal</t>
+          <t>Marzieh Bitaab</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4897,18 +4897,18 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Gail-Joon Ahn</t>
+          <t>Alireza Karimi</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ruoyu Wang 0001</t>
+          <t>Zhuoer Lyu</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Tiffany Bao</t>
+          <t>Adam Oest</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4966,18 +4966,18 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Yan Shoshitaishvili</t>
+          <t>Dhruv Kuchhal</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4989,18 +4989,18 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Adam Doupé</t>
+          <t>Gail-Joon Ahn</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Zeyu Lei</t>
+          <t>Ruoyu Wang 0001</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5031,22 +5031,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
+          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Güliz Seray Tuncay</t>
+          <t>Tiffany Bao</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5054,22 +5054,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
+          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Beatrice Carissa Williem</t>
+          <t>Yan Shoshitaishvili</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5077,22 +5077,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
+          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>Adam Doupé</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
+          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Zeyu Lei</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Adil Ahmad</t>
+          <t>Güliz Seray Tuncay</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5146,22 +5146,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>NDSS-Secure Data Analytics in Apache Spark with Fine-grained Policy Enforcement and Isolated Execution.</t>
+          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Justin Furuness</t>
+          <t>Beatrice Carissa Williem</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5169,22 +5169,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
+          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Cameron Morris</t>
+          <t>Z. Berkay Celik</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
+          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Reynaldo Morillo</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5215,22 +5215,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
+          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Arvind Kasiliya</t>
+          <t>Adil Ahmad</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5238,22 +5238,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
+          <t>NDSS-Secure Data Analytics in Apache Spark with Fine-grained Policy Enforcement and Isolated Execution.</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Bing Wang 0001</t>
+          <t>Justin Furuness</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Amir Herzberg</t>
+          <t>Cameron Morris</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Kangjie Lu</t>
+          <t>Reynaldo Morillo</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5307,22 +5307,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>NDSS-Sheep's Clothing, Wolf's Data: Detecting Server-Induced Client Vulnerabilities in Windows Remote IPC.</t>
+          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Seyed Mohammad Mehdi Mirnajafizadeh</t>
+          <t>Arvind Kasiliya</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5330,22 +5330,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>NDSS-SketchFeature: High-Quality Per-Flow Feature Extractor Towards Security-Aware Data Plane.</t>
+          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Wayne State University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Rhongho Jang</t>
+          <t>Bing Wang 0001</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5353,22 +5353,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>NDSS-SketchFeature: High-Quality Per-Flow Feature Extractor Towards Security-Aware Data Plane.</t>
+          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Wayne State University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ting Wang 0004</t>
+          <t>Amir Herzberg</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5376,22 +5376,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>NDSS-SongBsAb: A Dual Prevention Approach against Singing Voice Conversion based Illegal Song Covers.</t>
+          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Reham Mohamed Aburas</t>
+          <t>Kangjie Lu</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5399,22 +5399,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>NDSS-Speak Up, I'm Listening: Extracting Speech from Zero-Permission VR Sensors.</t>
+          <t>NDSS-Sheep's Clothing, Wolf's Data: Detecting Server-Induced Client Vulnerabilities in Windows Remote IPC.</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>American University of Sharjah</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>Seyed Mohammad Mehdi Mirnajafizadeh</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5422,22 +5422,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>NDSS-Speak Up, I'm Listening: Extracting Speech from Zero-Permission VR Sensors.</t>
+          <t>NDSS-SketchFeature: High-Quality Per-Flow Feature Extractor Towards Security-Aware Data Plane.</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Wayne State University</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Chuhong Yuan</t>
+          <t>Rhongho Jang</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5445,22 +5445,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
+          <t>NDSS-SketchFeature: High-Quality Per-Flow Feature Extractor Towards Security-Aware Data Plane.</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Wayne State University</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Ting Wang 0004</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
+          <t>NDSS-SongBsAb: A Dual Prevention Approach against Singing Voice Conversion based Illegal Song Covers.</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -5476,14 +5476,14 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Taesoo Kim</t>
+          <t>Reham Mohamed Aburas</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5491,22 +5491,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
+          <t>NDSS-Speak Up, I'm Listening: Extracting Speech from Zero-Permission VR Sensors.</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>American University of Sharjah</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Diwen Xue</t>
+          <t>Z. Berkay Celik</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5514,22 +5514,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
+          <t>NDSS-Speak Up, I'm Listening: Extracting Speech from Zero-Permission VR Sensors.</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Robert Stanley</t>
+          <t>Chuhong Yuan</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5537,22 +5537,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
+          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Piyush Kumar</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5560,22 +5560,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
+          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Roya Ensafi</t>
+          <t>Taesoo Kim</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
+          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Boladji Vinny Adjibi</t>
+          <t>Diwen Xue</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
+          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -5614,14 +5614,14 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Athanasios Avgetidis</t>
+          <t>Robert Stanley</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
+          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -5637,14 +5637,14 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Manos Antonakakis</t>
+          <t>Piyush Kumar</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
+          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -5660,14 +5660,14 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Fabian Monrose</t>
+          <t>Roya Ensafi</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5675,22 +5675,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
+          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Lily Klucinec</t>
+          <t>Boladji Vinny Adjibi</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
+          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Mandy Lanyon</t>
+          <t>Athanasios Avgetidis</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5721,22 +5721,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
+          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Julie Downs</t>
+          <t>Manos Antonakakis</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5744,22 +5744,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
+          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Lorrie Faith Cranor</t>
+          <t>Michael D. Bailey</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5767,22 +5767,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
+          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Martin Schwarzl</t>
+          <t>Fabian Monrose</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5790,22 +5790,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>NDSS-TME-Box: Scalable In-Process Isolation through Intel TME-MK Memory Encryption.</t>
+          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Yan Pang</t>
+          <t>Elijah Robert Bouma-Sims</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
+          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -5821,14 +5821,14 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Aiping Xiong</t>
+          <t>Lily Klucinec</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
+          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -5844,14 +5844,14 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Penn State University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Mandy Lanyon</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
+          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Zelun Kong</t>
+          <t>Julie Downs</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5882,22 +5882,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
+          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Minkyung Park</t>
+          <t>Lorrie Faith Cranor</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5905,22 +5905,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
+          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Chung Hwan Kim</t>
+          <t>Martin Schwarzl</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
+          <t>NDSS-TME-Box: Scalable In-Process Isolation through Intel TME-MK Memory Encryption.</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Xiangzhe Xu</t>
+          <t>Yan Pang</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -5959,14 +5959,14 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Zhuo Zhang 0002</t>
+          <t>Aiping Xiong</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -5982,14 +5982,14 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Penn State University</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Zian Su</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5997,22 +5997,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Ziyang Huang 0004</t>
+          <t>Zelun Kong</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6020,22 +6020,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Shiwei Feng 0002</t>
+          <t>Minkyung Park</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Yapeng Ye</t>
+          <t>Chung Hwan Kim</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6066,22 +6066,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Nan Jiang 0012</t>
+          <t>Xiangzhe Xu</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Danning Xie</t>
+          <t>Zhuo Zhang 0002</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6116,7 +6116,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Siyuan Cheng 0005</t>
+          <t>Zian Su</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Lin Tan 0001</t>
+          <t>Ziyang Huang 0004</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Xiangyu Zhang 0001</t>
+          <t>Shiwei Feng 0002</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Maryam Abbasihafshejani</t>
+          <t>Yapeng Ye</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6204,22 +6204,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>University of Texas at San Antonio</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Murtuza Jadliwala</t>
+          <t>Nan Jiang 0012</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6227,22 +6227,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>University of Texas at San Antonio</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Jinhao Zhu</t>
+          <t>Danning Xie</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6250,22 +6250,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>NDSS-VulShield: Protecting Vulnerable Code Before Deploying Patches.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>UC Berkeley</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Sena Sahin</t>
+          <t>Siyuan Cheng 0005</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6273,22 +6273,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Burak Sahin</t>
+          <t>Lin Tan 0001</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6296,22 +6296,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Frank Li 0001</t>
+          <t>Xiangyu Zhang 0001</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6319,36 +6319,174 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
+          <t>Maryam Abbasihafshejani</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>University of Texas at San Antonio</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Murtuza Jadliwala</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>5</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>University of Texas at San Antonio</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Jinhao Zhu</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>NDSS-VulShield: Protecting Vulnerable Code Before Deploying Patches.</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>2</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>UC Berkeley</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Sena Sahin</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Burak Sahin</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Frank Li 0001</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>2</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
           <t>Xiaoyan Sun 0003</t>
         </is>
       </c>
-      <c r="B258" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C258" t="inlineStr">
+      <c r="B264" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C264" t="inlineStr">
         <is>
           <t>NDSS-What's Done Is Not What's Claimed: Detecting and Interpreting Inconsistencies in App Behaviors.</t>
         </is>
       </c>
-      <c r="D258" t="n">
+      <c r="D264" t="n">
         <v>4</v>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E264" t="inlineStr">
         <is>
           <t>Department of Computer Science, Worcester Polytechnic Institute</t>
         </is>

--- a/Security-data/data/output/ndss_2025_us_institutions.xlsx
+++ b/Security-data/data/output/ndss_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E264"/>
+  <dimension ref="A1:E267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,7 +561,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Weiheng Bai</t>
+          <t>Yinggang Guo</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,18 +573,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>State Key Laboratory for Novel Software Technology, Nanjing University; University of Minnesota</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kangjie Lu</t>
+          <t>Weiheng Bai</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shang Ma</t>
+          <t>Kangjie Lu</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -615,22 +615,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NDSS-Careful About What App Promotion Ads Recommend! Detecting and Explaining Malware Promotion via App Promotion Graph.</t>
+          <t>NDSS-BULKHEAD: Secure, Scalable, and Efficient Kernel Compartmentalization with PKS.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>University of Notre Dame</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chaoran Chen</t>
+          <t>Shang Ma</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shao Yang</t>
+          <t>Chaoran Chen</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -665,18 +665,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Case Western Reserve University</t>
+          <t>University of Notre Dame</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shifu Hou</t>
+          <t>Shao Yang</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -688,18 +688,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>University of Notre Dame</t>
+          <t>Case Western Reserve University</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Toby Jia-Jun Li</t>
+          <t>Shifu Hou</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Xusheng Xiao</t>
+          <t>Toby Jia-Jun Li</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -734,18 +734,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Notre Dame</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Yanfang Ye 0001</t>
+          <t>Xusheng Xiao</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -757,18 +757,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>University of Notre Dame</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kaiyuan Zhang 0002</t>
+          <t>Yanfang Ye 0001</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -776,22 +776,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NDSS-CENSOR: Defense Against Gradient Inversion via Orthogonal Subspace Bayesian Sampling.</t>
+          <t>NDSS-Careful About What App Promotion Ads Recommend! Detecting and Explaining Malware Promotion via App Promotion Graph.</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Notre Dame</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Siyuan Cheng 0005</t>
+          <t>Kaiyuan Zhang 0002</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Guangyu Shen</t>
+          <t>Siyuan Cheng 0005</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bruno Ribeiro 0001</t>
+          <t>Guangyu Shen</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shengwei An</t>
+          <t>Bruno Ribeiro 0001</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pin-Yu Chen</t>
+          <t>Shengwei An</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -895,18 +895,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IBM Research AI</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Xiangyu Zhang 0001</t>
+          <t>Pin-Yu Chen</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -918,18 +918,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>IBM Research AI</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ninghui Li 0001</t>
+          <t>Xiangyu Zhang 0001</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sirus Shahini</t>
+          <t>Ninghui Li 0001</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -960,22 +960,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NDSS-CHAOS: Exploiting Station Time Synchronization in 802.11 Networks.</t>
+          <t>NDSS-CENSOR: Defense Against Gradient Inversion via Orthogonal Subspace Bayesian Sampling.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Robert Ricci</t>
+          <t>Sirus Shahini</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Xiaochen Li</t>
+          <t>Robert Ricci</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1006,22 +1006,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NDSS-Delay-allowed Differentially Private Data Stream Release.</t>
+          <t>NDSS-CHAOS: Exploiting Station Time Synchronization in 802.11 Networks.</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chen Gong 0005</t>
+          <t>Xiaochen Li</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shuya Feng</t>
+          <t>Chen Gong 0005</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1056,18 +1056,18 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Yuan Hong 0001</t>
+          <t>Shuya Feng</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Yuan Hong 0001</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1102,18 +1102,18 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yuefeng Peng</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NDSS-Diffence: Fencing Membership Privacy With Diffusion Models.</t>
+          <t>NDSS-Delay-allowed Differentially Private Data Stream Release.</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ali Naseh</t>
+          <t>Yuefeng Peng</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Ali Naseh</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Qiutong Men</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1190,22 +1190,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NDSS-Heimdall: Towards Risk-Aware Network Management Outsourcing.</t>
+          <t>NDSS-Diffence: Fencing Membership Privacy With Diffusion Models.</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Yongting Chen</t>
+          <t>Qiutong Men</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1217,18 +1217,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>New York University Shanghai</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jiajin Liu</t>
+          <t>Yongting Chen</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gengyu Chen</t>
+          <t>Jiajin Liu</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1263,18 +1263,18 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University Shanghai</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ying Zhang 0022</t>
+          <t>Gengyu Chen</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1286,18 +1286,18 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Vyas Sekar</t>
+          <t>Ying Zhang 0022</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1309,18 +1309,18 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Meta</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lingzhi Wang 0002</t>
+          <t>Vyas Sekar</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1328,22 +1328,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NDSS-Incorporating Gradients to Rules: Towards Lightweight, Adaptive Provenance-based Intrusion Detection.</t>
+          <t>NDSS-Heimdall: Towards Risk-Aware Network Management Outsourcing.</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Xiangmin Shen</t>
+          <t>Lingzhi Wang 0002</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Weijian Li 0002</t>
+          <t>Xiangmin Shen</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Han Liu 0001</t>
+          <t>Weijian Li 0002</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Yan Chen 0004</t>
+          <t>Han Liu 0001</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Maryam Rostamipoor</t>
+          <t>Yan Chen 0004</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1443,22 +1443,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NDSS-LeakLess: Selective Data Protection against Memory Leakage Attacks for Serverless Platforms.</t>
+          <t>NDSS-Incorporating Gradients to Rules: Towards Lightweight, Adaptive Provenance-based Intrusion Detection.</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Seyedhamed Ghavamnia</t>
+          <t>Maryam Rostamipoor</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1470,18 +1470,18 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Michalis Polychronakis</t>
+          <t>Seyedhamed Ghavamnia</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1493,18 +1493,18 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jung-Woo Chang</t>
+          <t>Michalis Polychronakis</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1512,22 +1512,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NDSS-Magmaw: Modality-Agnostic Adversarial Attacks on Machine Learning-Based Wireless Communication Systems.</t>
+          <t>NDSS-LeakLess: Selective Data Protection against Memory Leakage Attacks for Serverless Platforms.</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ke Sun 0012</t>
+          <t>Jung-Woo Chang</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nasimeh Heydaribeni</t>
+          <t>Ke Sun 0012</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Xinyu Zhang 0003</t>
+          <t>Nasimeh Heydaribeni</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Farinaz Koushanfar</t>
+          <t>Xinyu Zhang 0003</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ammar Askar</t>
+          <t>Farinaz Koushanfar</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NDSS-MALintent: Coverage Guided Intent Fuzzing Framework for Android.</t>
+          <t>NDSS-Magmaw: Modality-Agnostic Adversarial Attacks on Machine Learning-Based Wireless Communication Systems.</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Fabian Fleischer</t>
+          <t>Ammar Askar</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Christopher Kruegel</t>
+          <t>Fabian Fleischer</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1677,18 +1677,18 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>University of California, Santa Barbara</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Giovanni Vigna</t>
+          <t>Christopher Kruegel</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Taesoo Kim</t>
+          <t>Giovanni Vigna</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1723,18 +1723,18 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of California, Santa Barbara</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Taesoo Kim</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NDSS-Off-Path TCP Hijacking in Wi-Fi Networks: A Packet-Size Side Channel Attack.</t>
+          <t>NDSS-MALintent: Coverage Guided Intent Fuzzing Framework for Android.</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Takami Sato</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1765,22 +1765,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NDSS-On the Realism of LiDAR Spoofing Attacks against Autonomous Driving Vehicle at High Speed and Long Distance.</t>
+          <t>NDSS-Off-Path TCP Hijacking in Wi-Fi Networks: A Packet-Size Side Channel Attack.</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Qi Alfred Chen</t>
+          <t>Takami Sato</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Qi Alfred Chen</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1811,22 +1811,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NDSS-ReDAN: An Empirical Study on Remote DoS Attacks against NAT Networks.</t>
+          <t>NDSS-On the Realism of LiDAR Spoofing Attacks against Autonomous Driving Vehicle at High Speed and Long Distance.</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Xiaochen Zhu 0003</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1834,22 +1834,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NDSS-Revisiting EM-based Estimation for Locally Differentially Private Protocols.</t>
+          <t>NDSS-Passive Inference Attacks on Split Learning via Adversarial Regularization.</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>National University of Singapore &amp;amp; Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ningfei Wang</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1857,22 +1857,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NDSS-Revisiting Physical-World Adversarial Attack on Traffic Sign Recognition: A Commercial Systems Perspective.</t>
+          <t>NDSS-ReDAN: An Empirical Study on Remote DoS Attacks against NAT Networks.</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Shaoyuan Xie</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NDSS-Revisiting Physical-World Adversarial Attack on Traffic Sign Recognition: A Commercial Systems Perspective.</t>
+          <t>NDSS-Revisiting EM-based Estimation for Locally Differentially Private Protocols.</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1888,14 +1888,14 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Takami Sato</t>
+          <t>Ningfei Wang</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Yunpeng Luo</t>
+          <t>Shaoyuan Xie</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kaidi Xu</t>
+          <t>Takami Sato</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1953,18 +1953,18 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Drexel University</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Qi Alfred Chen</t>
+          <t>Yunpeng Luo</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Giuseppe La Manna</t>
+          <t>Kaidi Xu</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1995,22 +1995,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NDSS-Secret Spilling Drive: Leaking User Behavior through SSD Contention.</t>
+          <t>NDSS-Revisiting Physical-World Adversarial Attack on Traffic Sign Recognition: A Commercial Systems Perspective.</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Drexel University</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Eric Pauley</t>
+          <t>Qi Alfred Chen</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2018,22 +2018,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NDSS-Secure IP Address Allocation at Cloud Scale.</t>
+          <t>NDSS-Revisiting Physical-World Adversarial Attack on Traffic Sign Recognition: A Commercial Systems Perspective.</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kyle Domico</t>
+          <t>Giuseppe La Manna</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2041,22 +2041,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NDSS-Secure IP Address Allocation at Cloud Scale.</t>
+          <t>NDSS-Secret Spilling Drive: Leaking User Behavior through SSD Contention.</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Blaine Hoak</t>
+          <t>Eric Pauley</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ryan Sheatsley</t>
+          <t>Kyle Domico</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Quinn Burke 0002</t>
+          <t>Blaine Hoak</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Yohan Beugin</t>
+          <t>Ryan Sheatsley</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engin Kirda</t>
+          <t>Quinn Burke 0002</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2160,18 +2160,18 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Patrick D. McDaniel</t>
+          <t>Yohan Beugin</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jin Yao</t>
+          <t>Engin Kirda</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2202,22 +2202,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NDSS-TrajDeleter: Enabling Trajectory Forgetting in Offline Reinforcement Learning Agents.</t>
+          <t>NDSS-Secure IP Address Allocation at Cloud Scale.</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Patrick D. McDaniel</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NDSS-TrajDeleter: Enabling Trajectory Forgetting in Offline Reinforcement Learning Agents.</t>
+          <t>NDSS-Secure IP Address Allocation at Cloud Scale.</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Xiaoyuan Wu</t>
+          <t>Jin Yao</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2248,22 +2248,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NDSS-Transparency or Information Overload? Evaluating Users' Comprehension and Perceptions of the iOS App Privacy Report.</t>
+          <t>NDSS-TrajDeleter: Enabling Trajectory Forgetting in Offline Reinforcement Learning Agents.</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lydia Hu</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2271,22 +2271,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NDSS-Transparency or Information Overload? Evaluating Users' Comprehension and Perceptions of the iOS App Privacy Report.</t>
+          <t>NDSS-TrajDeleter: Enabling Trajectory Forgetting in Offline Reinforcement Learning Agents.</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Eric Zeng 0001</t>
+          <t>Xiaoyuan Wu</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Hana Habib</t>
+          <t>Lydia Hu</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Lujo Bauer</t>
+          <t>Eric Zeng 0001</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Yuqing Yang 0003</t>
+          <t>Hana Habib</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2363,22 +2363,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NDSS-Understanding Miniapp Malware: Identification, Dissection, and Characterization.</t>
+          <t>NDSS-Transparency or Information Overload? Evaluating Users' Comprehension and Perceptions of the iOS App Privacy Report.</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Yue Zhang 0025</t>
+          <t>Lujo Bauer</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NDSS-Understanding Miniapp Malware: Identification, Dissection, and Characterization.</t>
+          <t>NDSS-Transparency or Information Overload? Evaluating Users' Comprehension and Perceptions of the iOS App Privacy Report.</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Drexel University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Yuqing Yang 0003</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Hongwei Wu</t>
+          <t>Yue Zhang 0025</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NDSS-VeriBin: Adaptive Verification of Patches at the Binary Level.</t>
+          <t>NDSS-Understanding Miniapp Malware: Identification, Dissection, and Characterization.</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Drexel University</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ruoyu Wu</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NDSS-VeriBin: Adaptive Verification of Patches at the Binary Level.</t>
+          <t>NDSS-Understanding Miniapp Malware: Identification, Dissection, and Characterization.</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2463,14 +2463,14 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ayushi Sharma</t>
+          <t>Hongwei Wu</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Aravind Machiry</t>
+          <t>Ruoyu Wu</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Ayushi Sharma</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jackson Sippe</t>
+          <t>Aravind Machiry</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NDSS-Wallbleed: A Memory Disclosure Vulnerability in the Great Firewall of China.</t>
+          <t>NDSS-VeriBin: Adaptive Verification of Patches at the Binary Level.</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>University of Colorado Boulder</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Jade Sheffey</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NDSS-Wallbleed: A Memory Disclosure Vulnerability in the Great Firewall of China.</t>
+          <t>NDSS-VeriBin: Adaptive Verification of Patches at the Binary Level.</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UMass Amherst</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Jackson Sippe</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2597,18 +2597,18 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>UMass Amherst</t>
+          <t>University of Colorado Boulder</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Eric Wustrow</t>
+          <t>Jade Sheffey</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2620,18 +2620,18 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>University of Colorado Boulder</t>
+          <t>UMass Amherst</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Stijn Pletinckx</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2639,22 +2639,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NDSS-A Large-Scale Measurement Study of the PROXY Protocol and its Security Implications.</t>
+          <t>NDSS-Wallbleed: A Memory Disclosure Vulnerability in the Great Firewall of China.</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>University of California, Santa Barbara</t>
+          <t>UMass Amherst</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Christopher Kruegel</t>
+          <t>Eric Wustrow</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2662,22 +2662,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NDSS-A Large-Scale Measurement Study of the PROXY Protocol and its Security Implications.</t>
+          <t>NDSS-Wallbleed: A Memory Disclosure Vulnerability in the Great Firewall of China.</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>University of California, Santa Barbara</t>
+          <t>University of Colorado Boulder</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Giovanni Vigna</t>
+          <t>Stijn Pletinckx</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mahsa Bastankhah</t>
+          <t>Christopher Kruegel</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2708,22 +2708,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NDSS-Alba: The Dawn of Scalable Bridges for Blockchains.</t>
+          <t>NDSS-A Large-Scale Measurement Study of the PROXY Protocol and its Security Implications.</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of California, Santa Barbara</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Dominik Wermke</t>
+          <t>Giovanni Vigna</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NDSS-Attributing Open-Source Contributions is Critical but Difficult: A Systematic Analysis of GitHub Practices and Their Impact on Software Supply Chain Security.</t>
+          <t>NDSS-A Large-Scale Measurement Study of the PROXY Protocol and its Security Implications.</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>University of California, Santa Barbara</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Linxi Jiang</t>
+          <t>Mahsa Bastankhah</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NDSS-Beyond Classification: Inferring Function Names in Stripped Binaries via Domain Adapted LLMs.</t>
+          <t>NDSS-Alba: The Dawn of Scalable Bridges for Blockchains.</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Xin Jin</t>
+          <t>Dominik Wermke</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2777,22 +2777,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NDSS-Beyond Classification: Inferring Function Names in Stripped Binaries via Domain Adapted LLMs.</t>
+          <t>NDSS-Attributing Open-Source Contributions is Critical but Difficult: A Systematic Analysis of GitHub Practices and Their Impact on Software Supply Chain Security.</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Linxi Jiang</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ming Zhao</t>
+          <t>Xin Jin</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NDSS-Blackbox Fuzzing of Distributed Systems with Multi-Dimensional Inputs and Symmetry-Based Feedback Pruning.</t>
+          <t>NDSS-Beyond Classification: Inferring Function Names in Stripped Binaries via Domain Adapted LLMs.</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Caihua Li</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2846,22 +2846,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NDSS-Blindfold: Confidential Memory Management by Untrusted Operating System.</t>
+          <t>NDSS-Beyond Classification: Inferring Function Names in Stripped Binaries via Domain Adapted LLMs.</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Seung-Seob Lee</t>
+          <t>Ming Zhao</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2869,22 +2869,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NDSS-Blindfold: Confidential Memory Management by Untrusted Operating System.</t>
+          <t>NDSS-Blackbox Fuzzing of Distributed Systems with Multi-Dimensional Inputs and Symmetry-Based Feedback Pruning.</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Lin Zhong 0001</t>
+          <t>Caihua Li</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Magdalena Pasternak</t>
+          <t>Seung-Seob Lee</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2915,22 +2915,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NDSS-Characterizing the Impact of Audio Deepfakes in the Presence of Cochlear Implant.</t>
+          <t>NDSS-Blindfold: Confidential Memory Management by Untrusted Operating System.</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Kevin Warren</t>
+          <t>Lin Zhong 0001</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2938,22 +2938,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NDSS-Characterizing the Impact of Audio Deepfakes in the Presence of Cochlear Implant.</t>
+          <t>NDSS-Blindfold: Confidential Memory Management by Untrusted Operating System.</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Daniel Olszewski</t>
+          <t>Magdalena Pasternak</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Susan Nittrouer</t>
+          <t>Kevin Warren</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Patrick Traynor</t>
+          <t>Daniel Olszewski</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kevin R. B. Butler</t>
+          <t>Susan Nittrouer</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Chaithanya Naik Mude</t>
+          <t>Patrick Traynor</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3053,22 +3053,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NDSS-Crosstalk-induced Side Channel Threats in Multi-Tenant NISQ Computers.</t>
+          <t>NDSS-Characterizing the Impact of Audio Deepfakes in the Presence of Cochlear Implant.</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sanjay Das</t>
+          <t>Kevin R. B. Butler</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NDSS-Crosstalk-induced Side Channel Threats in Multi-Tenant NISQ Computers.</t>
+          <t>NDSS-Characterizing the Impact of Audio Deepfakes in the Presence of Cochlear Implant.</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Preetham Chandra Tikkireddi</t>
+          <t>Chaithanya Naik Mude</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Swamit Tannu</t>
+          <t>Sanjay Das</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3126,18 +3126,18 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>University of Wisconsin, Madison</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kanad Basu</t>
+          <t>Preetham Chandra Tikkireddi</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3149,18 +3149,18 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>University of Wisconsin-Madison</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Christopher Ellis</t>
+          <t>Swamit Tannu</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3168,22 +3168,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NDSS-Deanonymizing Device Identities via Side-channel Attacks in Exclusive-use IoTs &amp; Mitigation.</t>
+          <t>NDSS-Crosstalk-induced Side Channel Threats in Multi-Tenant NISQ Computers.</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Wisconsin, Madison</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Yue Zhang 0025</t>
+          <t>Kanad Basu</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NDSS-Deanonymizing Device Identities via Side-channel Attacks in Exclusive-use IoTs &amp; Mitigation.</t>
+          <t>NDSS-Crosstalk-induced Side Channel Threats in Multi-Tenant NISQ Computers.</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Drexel University</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Mohit Kumar Jangid</t>
+          <t>Christopher Ellis</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Shixuan Zhao 0002</t>
+          <t>Yue Zhang 0025</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3241,18 +3241,18 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Drexel University</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Mohit Kumar Jangid</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Md. Armanuzzaman</t>
+          <t>Shixuan Zhao 0002</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3283,22 +3283,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NDSS-Defending Against Membership Inference Attacks on Iteratively Pruned Deep Neural Networks.</t>
+          <t>NDSS-Deanonymizing Device Identities via Side-channel Attacks in Exclusive-use IoTs &amp; Mitigation.</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ziming Zhao 0001</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NDSS-Defending Against Membership Inference Attacks on Iteratively Pruned Deep Neural Networks.</t>
+          <t>NDSS-Deanonymizing Device Identities via Side-channel Attacks in Exclusive-use IoTs &amp; Mitigation.</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tyler Tucker</t>
+          <t>Md. Armanuzzaman</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3329,22 +3329,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
+          <t>NDSS-Defending Against Membership Inference Attacks on Iteratively Pruned Deep Neural Networks.</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Nathaniel Bennett</t>
+          <t>Ziming Zhao 0001</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
+          <t>NDSS-Defending Against Membership Inference Attacks on Iteratively Pruned Deep Neural Networks.</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Kevin R. B. Butler</t>
+          <t>Tyler Tucker</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Patrick Traynor</t>
+          <t>Nathaniel Bennett</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Peng Liu 0005</t>
+          <t>Kevin R. B. Butler</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NDSS-Eclipse Attacks on Monero's Peer-to-Peer Network.</t>
+          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Penn State University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Omar Alrawi</t>
+          <t>Patrick Traynor</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3444,22 +3444,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NDSS-Evaluating Machine Learning-Based IoT Device Identification Models for Security Applications.</t>
+          <t>NDSS-Detecting IMSI-Catchers by Characterizing Identity Exposing Messages in Cellular Traffic.</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Connor Glosner</t>
+          <t>Peng Liu 0005</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3467,22 +3467,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NDSS-FUZZUER: Enabling Fuzzing of UEFI Interfaces on EDK-2.</t>
+          <t>NDSS-Eclipse Attacks on Monero's Peer-to-Peer Network.</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Penn State University</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Aravind Machiry</t>
+          <t>Omar Alrawi</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NDSS-FUZZUER: Enabling Fuzzing of UEFI Interfaces on EDK-2.</t>
+          <t>NDSS-Evaluating Machine Learning-Based IoT Device Identification Models for Security Applications.</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -3498,14 +3498,14 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Qi Ling</t>
+          <t>Connor Glosner</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NDSS-GadgetMeter: Quantitatively and Accurately Gauging the Exploitability of Speculative Gadgets.</t>
+          <t>NDSS-FUZZUER: Enabling Fuzzing of UEFI Interfaces on EDK-2.</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -3528,7 +3528,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Baris Kasikci</t>
+          <t>Aravind Machiry</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NDSS-GadgetMeter: Quantitatively and Accurately Gauging the Exploitability of Speculative Gadgets.</t>
+          <t>NDSS-FUZZUER: Enabling Fuzzing of UEFI Interfaces on EDK-2.</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>University of Washington and Google</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Xiaojiang Du</t>
+          <t>Qi Ling</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3559,22 +3559,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NDSS-Hidden and Lost Control: on Security Design Risks in IoT User-Facing Matter Controller.</t>
+          <t>NDSS-GadgetMeter: Quantitatively and Accurately Gauging the Exploitability of Speculative Gadgets.</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Runze Zhang</t>
+          <t>Baris Kasikci</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3582,22 +3582,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
+          <t>NDSS-GadgetMeter: Quantitatively and Accurately Gauging the Exploitability of Speculative Gadgets.</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Washington and Google</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mingxuan Yao</t>
+          <t>Xiaojiang Du</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3605,22 +3605,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
+          <t>NDSS-Hidden and Lost Control: on Security Design Risks in IoT User-Facing Matter Controller.</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Haichuan Xu</t>
+          <t>Runze Zhang</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Omar Alrawi</t>
+          <t>Mingxuan Yao</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Haichuan Xu</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Corban Villa</t>
+          <t>Omar Alrawi</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
+          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Constantine Doumanidis</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3720,22 +3720,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
+          <t>NDSS-Hitchhiking Vaccine: Enhancing Botnet Remediation With Remote Code Deployment Reuse.</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Hithem Lamri</t>
+          <t>Corban Villa</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Michail Maniatakos</t>
+          <t>Constantine Doumanidis</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Franziska Roesner</t>
+          <t>Hithem Lamri</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NDSS-IsolateGPT: An Execution Isolation Architecture for LLM-Based Agentic Systems.</t>
+          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tadayoshi Kohno</t>
+          <t>Michail Maniatakos</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3812,22 +3812,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>NDSS-IsolateGPT: An Execution Isolation Architecture for LLM-Based Agentic Systems.</t>
+          <t>NDSS-ICSQuartz: Scan Cycle-Aware and Vendor-Agnostic Fuzzing for Industrial Control Systems.</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Yue Xiao 0007</t>
+          <t>Franziska Roesner</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3835,22 +3835,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
+          <t>NDSS-IsolateGPT: An Execution Isolation Architecture for LLM-Based Agentic Systems.</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Dhilung Kirat</t>
+          <t>Tadayoshi Kohno</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
+          <t>NDSS-IsolateGPT: An Execution Isolation Architecture for LLM-Based Agentic Systems.</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Douglas Lee Schales</t>
+          <t>Yue Xiao 0007</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Jiyong Jang</t>
+          <t>Dhilung Kirat</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Piyush Kumar Sharma</t>
+          <t>Douglas Lee Schales</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3927,22 +3927,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NDSS-LAMP: Lightweight Approaches for Latency Minimization in Mixnets with Practical Deployment Considerations.</t>
+          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Kushal Babel</t>
+          <t>Jiyong Jang</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3950,22 +3950,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
+          <t>NDSS-JBomAudit: Assessing the Landscape, Compliance, and Security Implications of Java SBOMs.</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cornell Tech &amp;amp; IC3</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Andrey Chursin</t>
+          <t>Piyush Kumar Sharma</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
+          <t>NDSS-LAMP: Lightweight Approaches for Latency Minimization in Mixnets with Practical Deployment Considerations.</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -3981,14 +3981,14 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mysten Labs</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Anastasios Kichidis</t>
+          <t>Kushal Babel</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -4000,18 +4000,18 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mysten Labs</t>
+          <t>Cornell Tech &amp;amp; IC3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Arun Koshy</t>
+          <t>Andrey Chursin</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Mingwei Tian</t>
+          <t>Anastasios Kichidis</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Darion Cassel</t>
+          <t>Arun Koshy</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4065,22 +4065,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
+          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Mysten Labs</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Min-Chien Hsu</t>
+          <t>Mingwei Tian</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4088,22 +4088,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
+          <t>NDSS-Mysticeti: Reaching the Latency Limits with Uncertified DAGs.</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Mysten Labs</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ruben Martins</t>
+          <t>Darion Cassel</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Limin Jia 0001</t>
+          <t>Nuno Sabino</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4138,18 +4138,18 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>IST &amp;amp; CMU</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ninghui Li 0001</t>
+          <t>Min-Chien Hsu</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NDSS-On the Robustness of LDP Protocols for Numerical Attributes under Data Poisoning Attacks.</t>
+          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Wenhai Sun</t>
+          <t>Ruben Martins</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>NDSS-On the Robustness of LDP Protocols for Numerical Attributes under Data Poisoning Attacks.</t>
+          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -4188,14 +4188,14 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Purdue University, West Lafayette, USA</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Matthew Gregoire</t>
+          <t>Limin Jia 0001</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4203,22 +4203,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
+          <t>NDSS-NodeMedic-FINE: Automatic Detection and Exploit Synthesis for Node.js Vulnerabilities.</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Margaret Pierce</t>
+          <t>Ninghui Li 0001</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4226,22 +4226,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
+          <t>NDSS-On the Robustness of LDP Protocols for Numerical Attributes under Data Poisoning Attacks.</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Saba Eskandarian</t>
+          <t>Wenhai Sun</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4249,22 +4249,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
+          <t>NDSS-On the Robustness of LDP Protocols for Numerical Attributes under Data Poisoning Attacks.</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill</t>
+          <t>Purdue University, West Lafayette, USA</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Shixin Song</t>
+          <t>Matthew Gregoire</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
+          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -4280,14 +4280,14 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Joseph Zhang</t>
+          <t>Margaret Pierce</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
+          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mengjia Yan 0001</t>
+          <t>Saba Eskandarian</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
+          <t>NDSS-Onion Franking: Abuse Reports for Mix-Based Private Messaging.</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -4326,14 +4326,14 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ruyi Ding</t>
+          <t>Shixin Song</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
+          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -4349,14 +4349,14 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Tong Zhou 0002</t>
+          <t>Joseph Zhang</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
+          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -4372,14 +4372,14 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Lili Su</t>
+          <t>Mengjia Yan 0001</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
+          <t>NDSS-Oreo: Protecting ASLR Against Microarchitectural Attacks.</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -4395,14 +4395,14 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Aidong Adam Ding</t>
+          <t>Ruyi Ding</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Xiaolin Xu 0001</t>
+          <t>Tong Zhou 0002</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Yunsi Fei</t>
+          <t>Lili Su</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Dzung Pham 0002</t>
+          <t>Aidong Adam Ding</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4479,22 +4479,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
+          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Shreyas Kulkarni</t>
+          <t>Xiaolin Xu 0001</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4502,22 +4502,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
+          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Yunsi Fei</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
+          <t>NDSS-Probe-Me-Not: Protecting Pre-trained Encoders from Malicious Probing.</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Peng Liu 0005</t>
+          <t>Dzung Pham 0002</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4548,22 +4548,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NDSS-RContainer: A Secure Container Architecture through Extending ARM CCA Hardware Primitives.</t>
+          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>The Pennsylvania State University, USA</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Shengzhi Zhang</t>
+          <t>Shreyas Kulkarni</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4571,22 +4571,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NDSS-RContainer: A Secure Container Architecture through Extending ARM CCA Hardware Primitives.</t>
+          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Department of Computer Science, Metropolitan College, Boston University, USA</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Eduardo Chielle</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4594,22 +4594,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NDSS-Recurrent Private Set Intersection for Unbalanced Databases with Cuckoo Hashing and Leveled FHE.</t>
+          <t>NDSS-RAIFLE: Reconstruction Attacks on Interaction-based Federated Learning with Adversarial Data Manipulation.</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Michail Maniatakos</t>
+          <t>Peng Liu 0005</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4617,22 +4617,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NDSS-Recurrent Private Set Intersection for Unbalanced Databases with Cuckoo Hashing and Leveled FHE.</t>
+          <t>NDSS-RContainer: A Secure Container Architecture through Extending ARM CCA Hardware Primitives.</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>The Pennsylvania State University, USA</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Xin Jin</t>
+          <t>Shengzhi Zhang</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4640,22 +4640,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
+          <t>NDSS-RContainer: A Secure Container Architecture through Extending ARM CCA Hardware Primitives.</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Department of Computer Science, Metropolitan College, Boston University, USA</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Shiqing Ma</t>
+          <t>Eduardo Chielle</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4663,22 +4663,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
+          <t>NDSS-Recurrent Private Set Intersection for Unbalanced Databases with Cuckoo Hashing and Leveled FHE.</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Michail Maniatakos</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4686,22 +4686,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
+          <t>NDSS-Recurrent Private Set Intersection for Unbalanced Databases with Cuckoo Hashing and Leveled FHE.</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Patrick Zielinski</t>
+          <t>Xin Jin</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4709,22 +4709,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>NDSS-Rethinking Trust in Forge-Based Git Security.</t>
+          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Justin Cappos</t>
+          <t>Shiqing Ma</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>NDSS-Rethinking Trust in Forge-Based Git Security.</t>
+          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Adrian Shuai Li</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4755,22 +4755,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NDSS-Revisiting Concept Drift in Windows Malware Detection: Adaptation to Real Drifted Malware with Minimal Samples.</t>
+          <t>NDSS-Repurposing Neural Networks for Efficient Cryptographic Computation.</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Elisa Bertino</t>
+          <t>Patrick Zielinski</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NDSS-Revisiting Concept Drift in Windows Malware Detection: Adaptation to Real Drifted Malware with Minimal Samples.</t>
+          <t>NDSS-Rethinking Trust in Forge-Based Git Security.</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Shanghao Shi</t>
+          <t>Justin Cappos</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4801,22 +4801,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
+          <t>NDSS-Rethinking Trust in Forge-Based Git Security.</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Yang Xiao 0010</t>
+          <t>Adrian Shuai Li</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
+          <t>NDSS-Revisiting Concept Drift in Windows Malware Detection: Adaptation to Real Drifted Malware with Minimal Samples.</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>University of Kentucky</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Chaoyu Zhang</t>
+          <t>Elisa Bertino</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
+          <t>NDSS-Revisiting Concept Drift in Windows Malware Detection: Adaptation to Real Drifted Malware with Minimal Samples.</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -4855,14 +4855,14 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Yi Shi 0001</t>
+          <t>Shanghao Shi</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Marzieh Bitaab</t>
+          <t>Yang Xiao 0010</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4893,22 +4893,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
+          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Kentucky</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Alireza Karimi</t>
+          <t>Chaoyu Zhang</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4916,22 +4916,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
+          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Zhuoer Lyu</t>
+          <t>Yi Shi 0001</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4939,22 +4939,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
+          <t>NDSS-Scale-MIA: A Scalable Model Inversion Attack against Secure Federated Learning via Latent Space Reconstruction.</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Adam Oest</t>
+          <t>Marzieh Bitaab</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4966,18 +4966,18 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Dhruv Kuchhal</t>
+          <t>Alireza Karimi</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4989,18 +4989,18 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Gail-Joon Ahn</t>
+          <t>Zhuoer Lyu</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Ruoyu Wang 0001</t>
+          <t>Adam Oest</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5035,18 +5035,18 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Tiffany Bao</t>
+          <t>Dhruv Kuchhal</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5058,18 +5058,18 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Yan Shoshitaishvili</t>
+          <t>Gail-Joon Ahn</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5081,7 +5081,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Adam Doupé</t>
+          <t>Ruoyu Wang 0001</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Zeyu Lei</t>
+          <t>Tiffany Bao</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5123,22 +5123,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
+          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Güliz Seray Tuncay</t>
+          <t>Yan Shoshitaishvili</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5146,22 +5146,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
+          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Beatrice Carissa Williem</t>
+          <t>Adam Doupé</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5169,22 +5169,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
+          <t>NDSS-SCAMMAGNIFIER: Piercing the Veil of Fraudulent Shopping Website Campaigns.</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>Zeyu Lei</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Güliz Seray Tuncay</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5219,18 +5219,18 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Adil Ahmad</t>
+          <t>Beatrice Carissa Williem</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>NDSS-Secure Data Analytics in Apache Spark with Fine-grained Policy Enforcement and Isolated Execution.</t>
+          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -5246,14 +5246,14 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Justin Furuness</t>
+          <t>Z. Berkay Celik</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5261,22 +5261,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
+          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Cameron Morris</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
+          <t>NDSS-ScopeVerif: Analyzing the Security of Android's Scoped Storage via Differential Analysis.</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Reynaldo Morillo</t>
+          <t>Adil Ahmad</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
+          <t>NDSS-Secure Data Analytics in Apache Spark with Fine-grained Policy Enforcement and Isolated Execution.</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -5315,14 +5315,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Arvind Kasiliya</t>
+          <t>Justin Furuness</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Bing Wang 0001</t>
+          <t>Cameron Morris</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Amir Herzberg</t>
+          <t>Reynaldo Morillo</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Kangjie Lu</t>
+          <t>Arvind Kasiliya</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5399,22 +5399,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>NDSS-Sheep's Clothing, Wolf's Data: Detecting Server-Induced Client Vulnerabilities in Windows Remote IPC.</t>
+          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Seyed Mohammad Mehdi Mirnajafizadeh</t>
+          <t>Bing Wang 0001</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5422,22 +5422,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>NDSS-SketchFeature: High-Quality Per-Flow Feature Extractor Towards Security-Aware Data Plane.</t>
+          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Wayne State University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Rhongho Jang</t>
+          <t>Amir Herzberg</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5445,22 +5445,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>NDSS-SketchFeature: High-Quality Per-Flow Feature Extractor Towards Security-Aware Data Plane.</t>
+          <t>NDSS-Securing BGP ASAP: ASPA and other Post-ROV Defenses.</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Wayne State University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Ting Wang 0004</t>
+          <t>Kangjie Lu</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5468,22 +5468,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>NDSS-SongBsAb: A Dual Prevention Approach against Singing Voice Conversion based Illegal Song Covers.</t>
+          <t>NDSS-Sheep's Clothing, Wolf's Data: Detecting Server-Induced Client Vulnerabilities in Windows Remote IPC.</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Reham Mohamed Aburas</t>
+          <t>Seyed Mohammad Mehdi Mirnajafizadeh</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>NDSS-Speak Up, I'm Listening: Extracting Speech from Zero-Permission VR Sensors.</t>
+          <t>NDSS-SketchFeature: High-Quality Per-Flow Feature Extractor Towards Security-Aware Data Plane.</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -5499,14 +5499,14 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>American University of Sharjah</t>
+          <t>Wayne State University</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>Rhongho Jang</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5514,22 +5514,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>NDSS-Speak Up, I'm Listening: Extracting Speech from Zero-Permission VR Sensors.</t>
+          <t>NDSS-SketchFeature: High-Quality Per-Flow Feature Extractor Towards Security-Aware Data Plane.</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Wayne State University</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Chuhong Yuan</t>
+          <t>Ting Wang 0004</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5537,22 +5537,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
+          <t>NDSS-SongBsAb: A Dual Prevention Approach against Singing Voice Conversion based Illegal Song Covers.</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Reham Mohamed Aburas</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5560,22 +5560,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
+          <t>NDSS-Speak Up, I'm Listening: Extracting Speech from Zero-Permission VR Sensors.</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>American University of Sharjah</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Taesoo Kim</t>
+          <t>Z. Berkay Celik</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
+          <t>NDSS-Speak Up, I'm Listening: Extracting Speech from Zero-Permission VR Sensors.</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Diwen Xue</t>
+          <t>Chuhong Yuan</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5606,22 +5606,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
+          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Robert Stanley</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5629,22 +5629,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
+          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Piyush Kumar</t>
+          <t>Taesoo Kim</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5652,22 +5652,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
+          <t>NDSS-Statically Discover Cross-Entry Use-After-Free Vulnerabilities in the Linux Kernel.</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Roya Ensafi</t>
+          <t>Diwen Xue</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Boladji Vinny Adjibi</t>
+          <t>Robert Stanley</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
+          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Athanasios Avgetidis</t>
+          <t>Piyush Kumar</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5721,22 +5721,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
+          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Manos Antonakakis</t>
+          <t>Roya Ensafi</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5744,22 +5744,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
+          <t>NDSS-The Discriminative Power of Cross-layer RTTs in Fingerprinting Proxy Traffic.</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Michael D. Bailey</t>
+          <t>Boladji Vinny Adjibi</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Fabian Monrose</t>
+          <t>Athanasios Avgetidis</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Elijah Robert Bouma-Sims</t>
+          <t>Manos Antonakakis</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
+          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Lily Klucinec</t>
+          <t>Michael D. Bailey</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
+          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Mandy Lanyon</t>
+          <t>Fabian Monrose</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
+          <t>NDSS-The Guardians of Name Street: Studying the Defensive Registration Practices of the Fortune 500.</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Julie Downs</t>
+          <t>Elijah Robert Bouma-Sims</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Lorrie Faith Cranor</t>
+          <t>Lily Klucinec</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Martin Schwarzl</t>
+          <t>Mandy Lanyon</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>NDSS-TME-Box: Scalable In-Process Isolation through Intel TME-MK Memory Encryption.</t>
+          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Yan Pang</t>
+          <t>Julie Downs</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5951,22 +5951,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
+          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Aiping Xiong</t>
+          <t>Lorrie Faith Cranor</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5974,22 +5974,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
+          <t>NDSS-The Kids Are All Right: Investigating the Susceptibility of Teens and Adults to YouTube Giveaway Scams.</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Penn State University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Martin Schwarzl</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
+          <t>NDSS-TME-Box: Scalable In-Process Isolation through Intel TME-MK Memory Encryption.</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -6005,14 +6005,14 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Zelun Kong</t>
+          <t>Yan Pang</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
+          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -6028,14 +6028,14 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Minkyung Park</t>
+          <t>Aiping Xiong</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
+          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -6051,14 +6051,14 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>Penn State University</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Chung Hwan Kim</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6066,22 +6066,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
+          <t>NDSS-Towards Understanding Unsafe Video Generation.</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Xiangzhe Xu</t>
+          <t>Zelun Kong</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -6097,14 +6097,14 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Zhuo Zhang 0002</t>
+          <t>Minkyung Park</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -6120,14 +6120,14 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Zian Su</t>
+          <t>Chung Hwan Kim</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
+          <t>NDSS-TZ-DATASHIELD: Automated Data Protection for Embedded Systems via Data-Flow-Based Compartmentalization.</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ziyang Huang 0004</t>
+          <t>Xiangzhe Xu</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Shiwei Feng 0002</t>
+          <t>Zhuo Zhang 0002</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Yapeng Ye</t>
+          <t>Zian Su</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Nan Jiang 0012</t>
+          <t>Ziyang Huang 0004</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Danning Xie</t>
+          <t>Shiwei Feng 0002</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Siyuan Cheng 0005</t>
+          <t>Yapeng Ye</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Lin Tan 0001</t>
+          <t>Nan Jiang 0012</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Xiangyu Zhang 0001</t>
+          <t>Danning Xie</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Maryam Abbasihafshejani</t>
+          <t>Siyuan Cheng 0005</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6342,22 +6342,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>University of Texas at San Antonio</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Murtuza Jadliwala</t>
+          <t>Lin Tan 0001</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6365,22 +6365,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>University of Texas at San Antonio</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Jinhao Zhu</t>
+          <t>Xiangyu Zhang 0001</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6388,22 +6388,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>NDSS-VulShield: Protecting Vulnerable Code Before Deploying Patches.</t>
+          <t>NDSS-Unleashing the Power of Generative Model in Recovering Variable Names from Stripped Binary.</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>UC Berkeley</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Sena Sahin</t>
+          <t>Maryam Abbasihafshejani</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6411,22 +6411,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Texas at San Antonio</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Burak Sahin</t>
+          <t>Murtuza Jadliwala</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+          <t>NDSS-VoiceRadar: Voice Deepfake Detection using Micro-Frequency and Compositional Analysis.</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Texas at San Antonio</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Frank Li 0001</t>
+          <t>Jinhao Zhu</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+          <t>NDSS-VulShield: Protecting Vulnerable Code Before Deploying Patches.</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -6465,28 +6465,97 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>UC Berkeley</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
+          <t>Sena Sahin</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Burak Sahin</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Frank Li 0001</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>NDSS-Was This You? Investigating the Design Considerations for Suspicious Login Notifications.</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
           <t>Xiaoyan Sun 0003</t>
         </is>
       </c>
-      <c r="B264" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C264" t="inlineStr">
+      <c r="B267" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C267" t="inlineStr">
         <is>
           <t>NDSS-What's Done Is Not What's Claimed: Detecting and Interpreting Inconsistencies in App Behaviors.</t>
         </is>
       </c>
-      <c r="D264" t="n">
+      <c r="D267" t="n">
         <v>4</v>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E267" t="inlineStr">
         <is>
           <t>Department of Computer Science, Worcester Polytechnic Institute</t>
         </is>
